--- a/Archivos/Hoja de cálculo CHATBOT.xlsx
+++ b/Archivos/Hoja de cálculo CHATBOT.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="230">
   <si>
     <t>Método implementado</t>
   </si>
@@ -579,6 +579,9 @@
   </si>
   <si>
     <t>COP</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>Tiempo de calentamiento</t>
@@ -723,15 +726,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
     <numFmt numFmtId="180" formatCode="0.0"/>
+    <numFmt numFmtId="181" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -805,19 +809,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -964,7 +955,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="47">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1105,12 +1096,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1124,12 +1109,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1153,12 +1132,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1172,12 +1145,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1201,12 +1168,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1220,12 +1181,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1617,17 +1572,26 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="25" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1636,132 +1600,123 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="25" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1785,9 +1740,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1819,9 +1771,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1949,7 +1898,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1977,9 +1925,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2049,9 +1994,6 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2064,9 +2006,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2082,9 +2021,6 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2098,14 +2034,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2148,9 +2080,6 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2189,9 +2118,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2223,7 +2149,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2234,9 +2160,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2271,16 +2194,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="180" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2304,9 +2223,6 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2345,9 +2261,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -2695,7 +2608,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:U95"/>
+  <dimension ref="A1:T95"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="33.2" style="1" customWidth="1"/>
@@ -2713,7 +2626,7 @@
     <col min="13" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:18">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2724,18 +2637,16 @@
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="186"/>
-      <c r="T1" s="186"/>
-    </row>
-    <row r="2" ht="15" spans="1:21">
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+    </row>
+    <row r="2" ht="15" spans="1:18">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2748,17 +2659,14 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
-      <c r="M2" s="146"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="186"/>
-      <c r="T2" s="186"/>
-      <c r="U2" s="186"/>
+      <c r="K2" s="136"/>
+      <c r="L2" s="136"/>
+      <c r="M2" s="136"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
     </row>
     <row r="3" ht="15" spans="1:18">
       <c r="A3" s="6" t="s">
@@ -2773,16 +2681,16 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
-      <c r="K3" s="147"/>
-      <c r="L3" s="147"/>
-      <c r="M3" s="147"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-    </row>
-    <row r="4" ht="48" customHeight="1" spans="1:21">
+      <c r="K3" s="137"/>
+      <c r="L3" s="137"/>
+      <c r="M3" s="137"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+    </row>
+    <row r="4" ht="48" customHeight="1" spans="1:18">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -2792,2314 +2700,2279 @@
       <c r="C4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
+      <c r="D4" s="9"/>
+      <c r="E4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="24">
-        <v>29</v>
-      </c>
-      <c r="J4" s="23" t="s">
+      <c r="I4" s="22">
+        <v>50</v>
+      </c>
+      <c r="J4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="148" t="s">
+      <c r="K4" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="149"/>
-      <c r="M4" s="149"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
-      <c r="S4" s="186"/>
-      <c r="T4" s="186"/>
-      <c r="U4" s="186"/>
-    </row>
-    <row r="5" ht="48" customHeight="1" spans="1:21">
-      <c r="A5" s="16"/>
+      <c r="L4" s="139"/>
+      <c r="M4" s="139"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+    </row>
+    <row r="5" ht="48" customHeight="1" spans="1:18">
+      <c r="A5" s="15"/>
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12" t="s">
+      <c r="D5" s="9"/>
+      <c r="E5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="150">
+      <c r="I5" s="140">
         <f>I4/D6</f>
-        <v>20</v>
+        <v>27.7777777777778</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="148" t="s">
+      <c r="K5" s="138" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="151"/>
-      <c r="M5" s="151"/>
-      <c r="N5" s="31"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="31"/>
-      <c r="S5" s="186"/>
-      <c r="T5" s="186"/>
-      <c r="U5" s="186"/>
-    </row>
-    <row r="6" ht="48" customHeight="1" spans="1:21">
-      <c r="A6" s="19"/>
-      <c r="B6" s="20" t="s">
+      <c r="L5" s="141"/>
+      <c r="M5" s="141"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:18">
+      <c r="A6" s="18"/>
+      <c r="B6" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="11">
-        <v>1.45</v>
-      </c>
-      <c r="E6" s="12" t="s">
+      <c r="D6" s="9">
+        <v>1.8</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="152">
+      <c r="J6" s="142">
         <v>0.75</v>
       </c>
-      <c r="K6" s="40" t="s">
+      <c r="K6" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="31"/>
-      <c r="R6" s="31"/>
-      <c r="S6" s="186"/>
-      <c r="T6" s="186"/>
-      <c r="U6" s="186"/>
-    </row>
-    <row r="7" ht="48" customHeight="1" spans="1:21">
-      <c r="A7" s="22" t="s">
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:18">
+      <c r="A7" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="22">
+        <v>30</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="153">
+      <c r="I7" s="19">
         <v>86</v>
       </c>
-      <c r="J7" s="20" t="s">
+      <c r="J7" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="K7" s="148" t="s">
+      <c r="K7" s="138" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="186"/>
-      <c r="T7" s="186"/>
-      <c r="U7" s="186"/>
-    </row>
-    <row r="8" ht="48" customHeight="1" spans="1:21">
-      <c r="A8" s="27"/>
-      <c r="B8" s="17" t="s">
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+    </row>
+    <row r="8" ht="48" customHeight="1" spans="1:18">
+      <c r="A8" s="25"/>
+      <c r="B8" s="16" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="11">
-        <v>10</v>
-      </c>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="9">
+        <v>12</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="H8" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="20" t="s">
+      <c r="J8" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="K8" s="154" t="s">
+      <c r="K8" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="31"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="31"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="186"/>
-      <c r="T8" s="186"/>
-      <c r="U8" s="186"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="29"/>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:18">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="155"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
-    </row>
-    <row r="10" ht="25.5" customHeight="1" spans="1:21">
-      <c r="A10" s="32" t="s">
+      <c r="A9" s="26"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="144"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+    </row>
+    <row r="10" ht="25.5" customHeight="1" spans="1:18">
+      <c r="A10" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="186"/>
-      <c r="T10" s="186"/>
-      <c r="U10" s="186"/>
-    </row>
-    <row r="11" ht="48" customHeight="1" spans="11:21">
-      <c r="K11" s="156"/>
-      <c r="L11" s="147"/>
-      <c r="M11" s="147"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="31"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="31"/>
-      <c r="S11" s="186"/>
-      <c r="T11" s="186"/>
-      <c r="U11" s="186"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29"/>
+    </row>
+    <row r="11" ht="48" customHeight="1" spans="11:18">
+      <c r="K11" s="145"/>
+      <c r="L11" s="137"/>
+      <c r="M11" s="137"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29"/>
     </row>
     <row r="12" ht="31.5" customHeight="1" spans="1:18">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="34" t="s">
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="157"/>
-      <c r="L12" s="158"/>
-      <c r="M12" s="158"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="31"/>
-    </row>
-    <row r="13" ht="64.5" customHeight="1" spans="1:21">
-      <c r="A13" s="36" t="s">
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="146"/>
+      <c r="L12" s="147"/>
+      <c r="M12" s="147"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="29"/>
+    </row>
+    <row r="13" ht="64.5" customHeight="1" spans="1:18">
+      <c r="A13" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="37">
         <v>2400</v>
       </c>
-      <c r="E13" s="40" t="s">
+      <c r="E13" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="38" t="s">
+      <c r="H13" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="I13" s="159">
+      <c r="I13" s="148">
         <v>1</v>
       </c>
-      <c r="J13" s="40" t="s">
+      <c r="J13" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="K13" s="149"/>
-      <c r="L13" s="149"/>
-      <c r="M13" s="149"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="160"/>
-      <c r="P13" s="160"/>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="186"/>
-      <c r="T13" s="186"/>
-      <c r="U13" s="186"/>
+      <c r="K13" s="139"/>
+      <c r="L13" s="139"/>
+      <c r="M13" s="139"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="149"/>
+      <c r="P13" s="149"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
     </row>
     <row r="14" ht="64.5" customHeight="1" spans="1:18">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="37">
         <f>610.78*EXP((17.269*D7)/(D7+237.3))</f>
-        <v>4005.11025920552</v>
-      </c>
-      <c r="E14" s="40" t="s">
+        <v>4242.44995258475</v>
+      </c>
+      <c r="E14" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="F14" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="38" t="s">
+      <c r="H14" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="I14" s="159">
+      <c r="I14" s="148">
         <f>5.8+(4.1*0.8)</f>
         <v>9.08</v>
       </c>
-      <c r="J14" s="40" t="s">
+      <c r="J14" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="31"/>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="31"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
     </row>
     <row r="15" ht="64.5" customHeight="1" spans="1:20">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="37">
         <f>610.78*EXP((17.269*D8)/(D8+237.3))</f>
-        <v>1227.87275885556</v>
-      </c>
-      <c r="E15" s="40" t="s">
+        <v>1402.45043931191</v>
+      </c>
+      <c r="E15" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="41" t="s">
+      <c r="F15" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="42" t="s">
+      <c r="G15" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="H15" s="38" t="s">
+      <c r="H15" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="I15" s="159">
+      <c r="I15" s="148">
         <f>D7-D8</f>
-        <v>19</v>
-      </c>
-      <c r="J15" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="T15" s="187"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="T15" s="173"/>
     </row>
     <row r="16" ht="64.5" customHeight="1" spans="1:20">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="42">
         <f>(I7/100)*D15</f>
-        <v>1055.97057261578</v>
-      </c>
-      <c r="E16" s="40" t="s">
+        <v>1206.10737780825</v>
+      </c>
+      <c r="E16" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="43" t="s">
+      <c r="F16" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="37" t="s">
+      <c r="G16" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="H16" s="38" t="s">
+      <c r="H16" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="I16" s="161">
+      <c r="I16" s="150">
         <f>(I5*I14*I15*I13)/1000</f>
-        <v>3.4504</v>
-      </c>
-      <c r="J16" s="40" t="s">
+        <v>4.54</v>
+      </c>
+      <c r="J16" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="31"/>
-      <c r="T16" s="187"/>
-    </row>
-    <row r="17" ht="64.5" customHeight="1" spans="1:21">
-      <c r="A17" s="36" t="s">
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="T16" s="173"/>
+    </row>
+    <row r="17" ht="64.5" customHeight="1" spans="1:18">
+      <c r="A17" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="37">
         <f>(D14-D15)/1000</f>
-        <v>2.77723750034996</v>
-      </c>
-      <c r="E17" s="40" t="s">
+        <v>2.83999951327283</v>
+      </c>
+      <c r="E17" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="46" t="s">
+      <c r="F17" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="186"/>
-      <c r="T17" s="186"/>
-      <c r="U17" s="186"/>
-    </row>
-    <row r="18" ht="64.5" customHeight="1" spans="1:21">
-      <c r="A18" s="36" t="s">
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+    </row>
+    <row r="18" ht="64.5" customHeight="1" spans="1:18">
+      <c r="A18" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="37">
         <f>(0.089+0.078*0.8)*D17*I5</f>
-        <v>8.40947515105967</v>
-      </c>
-      <c r="E18" s="40" t="s">
+        <v>11.9437757308196</v>
+      </c>
+      <c r="E18" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="F18" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="G18" s="37" t="s">
+      <c r="G18" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="H18" s="36" t="s">
+      <c r="H18" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="I18" s="162">
+      <c r="I18" s="151">
         <f>(SUM(D27,D19,I16))*0.2</f>
-        <v>2.50519269055228</v>
-      </c>
-      <c r="J18" s="40" t="s">
+        <v>3.45333316583035</v>
+      </c>
+      <c r="J18" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="K18" s="31"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="31"/>
-      <c r="P18" s="31"/>
-      <c r="Q18" s="31"/>
-      <c r="R18" s="31"/>
-      <c r="S18" s="186"/>
-      <c r="T18" s="186"/>
-      <c r="U18" s="186"/>
-    </row>
-    <row r="19" ht="64.5" customHeight="1" spans="1:21">
-      <c r="A19" s="47" t="s">
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+    </row>
+    <row r="19" ht="64.5" customHeight="1" spans="1:18">
+      <c r="A19" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="49" t="s">
+      <c r="C19" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="50">
+      <c r="D19" s="48">
         <f>(D13*D18)/3600</f>
-        <v>5.60631676737311</v>
-      </c>
-      <c r="E19" s="51" t="s">
+        <v>7.96251715387976</v>
+      </c>
+      <c r="E19" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="52"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="163"/>
-      <c r="J19" s="164"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="31"/>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="186"/>
-      <c r="T19" s="186"/>
-      <c r="U19" s="186"/>
-    </row>
-    <row r="20" ht="32.25" customHeight="1" spans="1:21">
-      <c r="A20" s="55" t="s">
+      <c r="F19" s="50"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="152"/>
+      <c r="J19" s="153"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+    </row>
+    <row r="20" ht="32.25" customHeight="1" spans="1:20">
+      <c r="A20" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="B20" s="55"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55" t="s">
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="55"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="186"/>
-      <c r="T20" s="188"/>
-      <c r="U20" s="186"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="T20" s="174"/>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="D21" s="44">
+      <c r="D21" s="42">
         <f>D7+273</f>
-        <v>302</v>
-      </c>
-      <c r="E21" s="40" t="s">
+        <v>303</v>
+      </c>
+      <c r="E21" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="56" t="s">
+      <c r="F21" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="G21" s="56" t="s">
+      <c r="G21" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="H21" s="56" t="s">
+      <c r="H21" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="I21" s="165">
+      <c r="I21" s="154">
         <f>SUM(D27,D19,I16,I18)</f>
-        <v>15.0311561433137</v>
-      </c>
-      <c r="J21" s="166" t="s">
+        <v>20.7199989949821</v>
+      </c>
+      <c r="J21" s="155" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="44">
+      <c r="D22" s="42">
         <f>D8+273</f>
-        <v>283</v>
-      </c>
-      <c r="E22" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="E22" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="167"/>
-      <c r="J22" s="168"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="156"/>
+      <c r="J22" s="157"/>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10">
-      <c r="A23" s="41" t="s">
+      <c r="A23" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="C23" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="44">
+      <c r="D23" s="42">
         <v>5.67e-8</v>
       </c>
-      <c r="E23" s="40" t="s">
+      <c r="E23" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F23" s="59" t="s">
+      <c r="F23" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C24" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="60">
+      <c r="D24" s="58">
         <f>D21^4</f>
-        <v>8318169616</v>
-      </c>
-      <c r="E24" s="40" t="s">
+        <v>8428892481</v>
+      </c>
+      <c r="E24" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="F24" s="43" t="s">
+      <c r="F24" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="G24" s="43" t="s">
+      <c r="G24" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="H24" s="61" t="s">
+      <c r="H24" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="I24" s="69">
+      <c r="I24" s="64">
         <v>4.18</v>
       </c>
-      <c r="J24" s="169" t="s">
+      <c r="J24" s="158" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="58" t="s">
+      <c r="B25" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="60">
+      <c r="D25" s="58">
         <f>D22^4</f>
-        <v>6414247921</v>
-      </c>
-      <c r="E25" s="40" t="s">
+        <v>6597500625</v>
+      </c>
+      <c r="E25" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="43" t="s">
+      <c r="F25" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="G25" s="43" t="s">
+      <c r="G25" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="H25" s="61" t="s">
+      <c r="H25" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="I25" s="69">
+      <c r="I25" s="64">
         <v>998</v>
       </c>
-      <c r="J25" s="169" t="s">
+      <c r="J25" s="158" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="58" t="s">
+      <c r="B26" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="D26" s="60">
+      <c r="D26" s="58">
         <f>D24-(0.8*D25)</f>
-        <v>3186771279.2</v>
-      </c>
-      <c r="E26" s="40" t="s">
+        <v>3150891981</v>
+      </c>
+      <c r="E26" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="F26" s="43" t="s">
+      <c r="F26" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="G26" s="43" t="s">
+      <c r="G26" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="H26" s="61" t="s">
+      <c r="H26" s="59" t="s">
         <v>112</v>
       </c>
-      <c r="I26" s="69">
+      <c r="I26" s="64">
         <f>D7-(D8-2)</f>
-        <v>21</v>
-      </c>
-      <c r="J26" s="169" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="158" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10">
-      <c r="A27" s="36" t="s">
+      <c r="A27" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="58" t="s">
+      <c r="B27" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="D27" s="44">
+      <c r="D27" s="42">
         <f>(I5*D23*0.96*D26)/1000</f>
-        <v>3.46924668538829</v>
-      </c>
-      <c r="E27" s="62" t="s">
+        <v>4.764148675272</v>
+      </c>
+      <c r="E27" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="F27" s="43" t="s">
+      <c r="F27" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="G27" s="43" t="s">
+      <c r="G27" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="H27" s="43" t="s">
+      <c r="H27" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="I27" s="161">
+      <c r="I27" s="150">
         <f>I4*I26*I25*I24/3600</f>
-        <v>705.702433333333</v>
-      </c>
-      <c r="J27" s="62" t="s">
+        <v>1158.78888888889</v>
+      </c>
+      <c r="J27" s="60" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1"/>
     <row r="29" ht="48" customHeight="1" spans="1:10">
-      <c r="A29" s="63" t="s">
+      <c r="A29" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="B29" s="63"/>
-      <c r="C29" s="63"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="64"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="64"/>
-      <c r="J29" s="64"/>
+      <c r="B29" s="61"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="62"/>
     </row>
     <row r="30" ht="33.75" customHeight="1" spans="1:10">
-      <c r="A30" s="65" t="s">
+      <c r="A30" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="B30" s="65"/>
-      <c r="C30" s="65"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="65"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
+      <c r="B30" s="63"/>
+      <c r="C30" s="63"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="63"/>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:10">
-      <c r="A31" s="61" t="s">
+      <c r="A31" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="66" t="s">
+      <c r="B31" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C31" s="67" t="s">
+      <c r="C31" s="65" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="68"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="61" t="s">
+      <c r="D31" s="66"/>
+      <c r="E31" s="64"/>
+      <c r="F31" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="G31" s="70" t="s">
+      <c r="G31" s="67" t="s">
         <v>124</v>
       </c>
-      <c r="H31" s="71" t="s">
+      <c r="H31" s="68" t="s">
         <v>123</v>
       </c>
-      <c r="I31" s="170"/>
-      <c r="J31" s="69"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="64"/>
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:10">
-      <c r="A32" s="41" t="s">
+      <c r="A32" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="72" t="s">
+      <c r="B32" s="69" t="s">
         <v>126</v>
       </c>
-      <c r="C32" s="73">
+      <c r="C32" s="70">
         <v>20</v>
       </c>
-      <c r="D32" s="74" t="s">
+      <c r="D32" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="E32" s="75" t="s">
+      <c r="E32" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="F32" s="41" t="s">
+      <c r="F32" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="G32" s="76">
+      <c r="G32" s="73">
         <v>7521008</v>
       </c>
-      <c r="H32" s="73">
+      <c r="H32" s="70">
         <v>20</v>
       </c>
-      <c r="I32" s="74" t="s">
+      <c r="I32" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="J32" s="75" t="s">
+      <c r="J32" s="72" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:10">
-      <c r="A33" s="41" t="s">
+      <c r="A33" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="B33" s="72" t="s">
+      <c r="B33" s="69" t="s">
         <v>129</v>
       </c>
-      <c r="C33" s="73">
+      <c r="C33" s="70">
         <v>30</v>
       </c>
-      <c r="D33" s="74" t="s">
+      <c r="D33" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="E33" s="75" t="s">
+      <c r="E33" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="F33" s="41" t="s">
+      <c r="F33" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="G33" s="76">
+      <c r="G33" s="73">
         <v>10605042</v>
       </c>
-      <c r="H33" s="73">
+      <c r="H33" s="70">
         <v>30</v>
       </c>
-      <c r="I33" s="74" t="s">
+      <c r="I33" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="J33" s="75" t="s">
+      <c r="J33" s="72" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:10">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="B34" s="72" t="s">
+      <c r="B34" s="69" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="73">
+      <c r="C34" s="70">
         <v>40</v>
       </c>
-      <c r="D34" s="74" t="s">
+      <c r="D34" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="75" t="s">
+      <c r="E34" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="F34" s="41" t="s">
+      <c r="F34" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="G34" s="76">
+      <c r="G34" s="73">
         <v>14411765</v>
       </c>
-      <c r="H34" s="73">
+      <c r="H34" s="70">
         <v>40</v>
       </c>
-      <c r="I34" s="74" t="s">
+      <c r="I34" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="J34" s="75" t="s">
+      <c r="J34" s="72" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:10">
-      <c r="A35" s="69"/>
-      <c r="B35" s="69"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
+      <c r="A35" s="64"/>
+      <c r="B35" s="64"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="64"/>
+      <c r="I35" s="64"/>
+      <c r="J35" s="64"/>
     </row>
     <row r="36" ht="34.5" customHeight="1" spans="1:10">
-      <c r="A36" s="77" t="s">
+      <c r="A36" s="74" t="s">
         <v>132</v>
       </c>
-      <c r="B36" s="65"/>
-      <c r="C36" s="65"/>
-      <c r="D36" s="65"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="65"/>
-      <c r="J36" s="171"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="159"/>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:10">
-      <c r="A37" s="43" t="s">
+      <c r="A37" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="B37" s="78" t="s">
+      <c r="B37" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="C37" s="73">
+      <c r="C37" s="70">
         <v>27</v>
       </c>
-      <c r="D37" s="79" t="s">
+      <c r="D37" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="E37" s="75" t="s">
+      <c r="E37" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="F37" s="43" t="s">
+      <c r="F37" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="G37" s="76">
+      <c r="G37" s="73">
         <v>10605042</v>
       </c>
-      <c r="H37" s="73">
+      <c r="H37" s="70">
         <v>27</v>
       </c>
-      <c r="I37" s="79" t="s">
+      <c r="I37" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="J37" s="75" t="s">
+      <c r="J37" s="72" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:10">
-      <c r="A38" s="43" t="s">
+      <c r="A38" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="B38" s="78" t="s">
+      <c r="B38" s="75" t="s">
         <v>137</v>
       </c>
-      <c r="C38" s="73">
+      <c r="C38" s="70">
         <v>40</v>
       </c>
-      <c r="D38" s="79" t="s">
+      <c r="D38" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="E38" s="75" t="s">
+      <c r="E38" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="F38" s="43" t="s">
+      <c r="F38" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="G38" s="76">
+      <c r="G38" s="73">
         <v>14411765</v>
       </c>
-      <c r="H38" s="73">
+      <c r="H38" s="70">
         <v>40</v>
       </c>
-      <c r="I38" s="79" t="s">
+      <c r="I38" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="J38" s="75" t="s">
+      <c r="J38" s="72" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" ht="48" customHeight="1" spans="1:10">
-      <c r="A39" s="80"/>
-      <c r="B39" s="81"/>
-      <c r="C39" s="82"/>
-      <c r="D39" s="82"/>
-      <c r="E39" s="82"/>
-      <c r="F39" s="80"/>
-      <c r="G39" s="83"/>
-      <c r="H39" s="82"/>
-      <c r="I39" s="82"/>
-      <c r="J39" s="172"/>
+      <c r="A39" s="76"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="160"/>
     </row>
     <row r="40" s="1" customFormat="1" ht="48" customHeight="1" spans="1:10">
-      <c r="A40" s="63" t="s">
+      <c r="A40" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="B40" s="63"/>
-      <c r="C40" s="63"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="64"/>
-      <c r="J40" s="64"/>
+      <c r="B40" s="61"/>
+      <c r="C40" s="61"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="62"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="48" customHeight="1" spans="1:10">
-      <c r="A41" s="55" t="s">
+      <c r="A41" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="B41" s="55"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55" t="s">
+      <c r="B41" s="53"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="G41" s="55"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="55"/>
-      <c r="J41" s="55"/>
+      <c r="G41" s="53"/>
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
     </row>
     <row r="42" s="1" customFormat="1" ht="48" customHeight="1" spans="1:10">
-      <c r="A42" s="43" t="s">
+      <c r="A42" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="B42" s="78" t="s">
+      <c r="B42" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="C42" s="73">
+      <c r="C42" s="70">
         <v>27</v>
       </c>
-      <c r="D42" s="79" t="s">
+      <c r="D42" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="E42" s="75" t="s">
+      <c r="E42" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="F42" s="43" t="s">
+      <c r="F42" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="G42" s="76">
+      <c r="G42" s="73">
         <v>10605042</v>
       </c>
-      <c r="H42" s="73">
+      <c r="H42" s="70">
         <v>27</v>
       </c>
-      <c r="I42" s="79" t="s">
+      <c r="I42" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="J42" s="75" t="s">
+      <c r="J42" s="72" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="48" customHeight="1" spans="1:11">
-      <c r="A43" s="43" t="s">
+      <c r="A43" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="B43" s="78" t="s">
+      <c r="B43" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="C43" s="73">
+      <c r="C43" s="70">
         <v>27</v>
       </c>
-      <c r="D43" s="79" t="s">
+      <c r="D43" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="E43" s="75" t="s">
+      <c r="E43" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="F43" s="43" t="s">
+      <c r="F43" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="G43" s="76">
+      <c r="G43" s="73">
         <v>10605042</v>
       </c>
-      <c r="H43" s="73">
+      <c r="H43" s="70">
         <v>27</v>
       </c>
-      <c r="I43" s="79" t="s">
+      <c r="I43" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="J43" s="75" t="s">
+      <c r="J43" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="K43" s="173"/>
+      <c r="K43" s="161"/>
     </row>
     <row r="44" s="1" customFormat="1" ht="48" customHeight="1" spans="1:11">
-      <c r="A44" s="84"/>
-      <c r="B44" s="85"/>
-      <c r="C44" s="86"/>
-      <c r="D44" s="86"/>
-      <c r="E44" s="86"/>
-      <c r="F44" s="84"/>
-      <c r="G44" s="87"/>
-      <c r="H44" s="86"/>
-      <c r="I44" s="86"/>
-      <c r="J44" s="86"/>
-      <c r="K44" s="173"/>
+      <c r="A44" s="80"/>
+      <c r="B44" s="81"/>
+      <c r="C44" s="82"/>
+      <c r="D44" s="82"/>
+      <c r="E44" s="82"/>
+      <c r="F44" s="80"/>
+      <c r="G44" s="83"/>
+      <c r="H44" s="82"/>
+      <c r="I44" s="82"/>
+      <c r="J44" s="82"/>
+      <c r="K44" s="161"/>
     </row>
     <row r="45" s="2" customFormat="1" ht="48" customHeight="1" spans="1:10">
-      <c r="A45" s="88" t="s">
+      <c r="A45" s="84" t="s">
         <v>141</v>
       </c>
-      <c r="B45" s="89"/>
-      <c r="C45" s="90"/>
-      <c r="D45" s="91" t="s">
+      <c r="B45" s="85"/>
+      <c r="C45" s="86"/>
+      <c r="D45" s="87" t="s">
         <v>142</v>
       </c>
-      <c r="E45" s="92"/>
-      <c r="F45" s="92"/>
-      <c r="G45" s="92"/>
-      <c r="H45" s="92"/>
-      <c r="I45" s="174"/>
-      <c r="J45" s="175"/>
+      <c r="E45" s="88"/>
+      <c r="F45" s="88"/>
+      <c r="G45" s="88"/>
+      <c r="H45" s="88"/>
+      <c r="I45" s="162"/>
+      <c r="J45" s="163"/>
     </row>
     <row r="46" ht="36.75" customHeight="1" spans="1:10">
-      <c r="A46" s="93"/>
-      <c r="B46" s="94"/>
-      <c r="C46" s="95"/>
-      <c r="D46" s="96" t="s">
+      <c r="A46" s="89"/>
+      <c r="B46" s="90"/>
+      <c r="C46" s="91"/>
+      <c r="D46" s="92" t="s">
         <v>143</v>
       </c>
-      <c r="E46" s="97"/>
-      <c r="F46" s="97"/>
-      <c r="G46" s="97" t="s">
+      <c r="E46" s="93"/>
+      <c r="F46" s="93"/>
+      <c r="G46" s="93" t="s">
         <v>144</v>
       </c>
-      <c r="H46" s="97"/>
-      <c r="I46" s="176"/>
-      <c r="J46" s="177"/>
+      <c r="H46" s="93"/>
+      <c r="I46" s="164"/>
+      <c r="J46" s="165"/>
     </row>
     <row r="47" ht="33" customHeight="1" spans="1:10">
-      <c r="A47" s="98" t="s">
+      <c r="A47" s="94" t="s">
         <v>145</v>
       </c>
-      <c r="B47" s="99"/>
-      <c r="C47" s="99"/>
-      <c r="D47" s="100" t="s">
+      <c r="B47" s="95"/>
+      <c r="C47" s="95"/>
+      <c r="D47" s="96" t="s">
         <v>145</v>
       </c>
-      <c r="E47" s="101"/>
-      <c r="F47" s="101"/>
-      <c r="G47" s="102" t="s">
+      <c r="E47" s="97"/>
+      <c r="F47" s="97"/>
+      <c r="G47" s="98" t="s">
         <v>146</v>
       </c>
-      <c r="H47" s="103"/>
-      <c r="I47" s="178"/>
-      <c r="J47" s="179"/>
+      <c r="H47" s="98"/>
+      <c r="I47" s="166"/>
+      <c r="J47" s="167"/>
     </row>
     <row r="48" ht="33" customHeight="1" spans="1:10">
-      <c r="A48" s="104" t="s">
+      <c r="A48" s="99" t="s">
         <v>147</v>
       </c>
-      <c r="B48" s="105"/>
-      <c r="C48" s="105"/>
-      <c r="D48" s="106" t="s">
+      <c r="B48" s="100"/>
+      <c r="C48" s="100"/>
+      <c r="D48" s="101" t="s">
         <v>148</v>
       </c>
-      <c r="E48" s="107"/>
-      <c r="F48" s="107"/>
-      <c r="G48" s="108" t="s">
+      <c r="E48" s="102"/>
+      <c r="F48" s="102"/>
+      <c r="G48" s="100" t="s">
         <v>149</v>
       </c>
-      <c r="H48" s="105"/>
-      <c r="I48" s="180"/>
-      <c r="J48" s="179"/>
+      <c r="H48" s="100"/>
+      <c r="I48" s="168"/>
+      <c r="J48" s="167"/>
     </row>
     <row r="49" ht="33" customHeight="1" spans="1:10">
-      <c r="A49" s="109" t="s">
+      <c r="A49" s="103" t="s">
         <v>150</v>
       </c>
-      <c r="B49" s="110"/>
-      <c r="C49" s="110"/>
-      <c r="D49" s="111" t="s">
+      <c r="B49" s="104"/>
+      <c r="C49" s="104"/>
+      <c r="D49" s="105" t="s">
         <v>151</v>
       </c>
-      <c r="E49" s="112"/>
-      <c r="F49" s="112"/>
-      <c r="G49" s="113" t="s">
+      <c r="E49" s="106"/>
+      <c r="F49" s="106"/>
+      <c r="G49" s="107" t="s">
         <v>152</v>
       </c>
-      <c r="H49" s="114"/>
-      <c r="I49" s="181"/>
-      <c r="J49" s="179"/>
+      <c r="H49" s="107"/>
+      <c r="I49" s="169"/>
+      <c r="J49" s="167"/>
     </row>
     <row r="50" ht="33" customHeight="1" spans="1:10">
-      <c r="A50" s="106" t="s">
+      <c r="A50" s="101" t="s">
         <v>153</v>
       </c>
-      <c r="B50" s="107"/>
-      <c r="C50" s="107"/>
-      <c r="D50" s="106" t="s">
+      <c r="B50" s="102"/>
+      <c r="C50" s="102"/>
+      <c r="D50" s="101" t="s">
         <v>150</v>
       </c>
-      <c r="E50" s="107"/>
-      <c r="F50" s="107"/>
-      <c r="G50" s="108" t="s">
+      <c r="E50" s="102"/>
+      <c r="F50" s="102"/>
+      <c r="G50" s="100" t="s">
         <v>154</v>
       </c>
-      <c r="H50" s="105"/>
-      <c r="I50" s="180"/>
-      <c r="J50" s="179"/>
+      <c r="H50" s="100"/>
+      <c r="I50" s="168"/>
+      <c r="J50" s="167"/>
     </row>
     <row r="51" ht="33" customHeight="1" spans="1:10">
-      <c r="A51" s="109" t="s">
+      <c r="A51" s="103" t="s">
         <v>155</v>
       </c>
-      <c r="B51" s="110"/>
-      <c r="C51" s="110"/>
-      <c r="D51" s="111" t="s">
+      <c r="B51" s="104"/>
+      <c r="C51" s="104"/>
+      <c r="D51" s="105" t="s">
         <v>156</v>
       </c>
-      <c r="E51" s="112"/>
-      <c r="F51" s="112"/>
-      <c r="G51" s="113" t="s">
+      <c r="E51" s="106"/>
+      <c r="F51" s="106"/>
+      <c r="G51" s="107" t="s">
         <v>157</v>
       </c>
-      <c r="H51" s="114"/>
-      <c r="I51" s="181"/>
-      <c r="J51" s="179"/>
+      <c r="H51" s="107"/>
+      <c r="I51" s="169"/>
+      <c r="J51" s="167"/>
     </row>
     <row r="52" ht="33" customHeight="1" spans="1:10">
-      <c r="A52" s="106" t="s">
+      <c r="A52" s="101" t="s">
         <v>158</v>
       </c>
-      <c r="B52" s="107"/>
-      <c r="C52" s="107"/>
-      <c r="D52" s="106" t="s">
+      <c r="B52" s="102"/>
+      <c r="C52" s="102"/>
+      <c r="D52" s="101" t="s">
         <v>159</v>
       </c>
-      <c r="E52" s="107"/>
-      <c r="F52" s="107"/>
-      <c r="G52" s="108" t="s">
+      <c r="E52" s="102"/>
+      <c r="F52" s="102"/>
+      <c r="G52" s="100" t="s">
         <v>160</v>
       </c>
-      <c r="H52" s="105"/>
-      <c r="I52" s="180"/>
-      <c r="J52" s="179"/>
+      <c r="H52" s="100"/>
+      <c r="I52" s="168"/>
+      <c r="J52" s="167"/>
     </row>
     <row r="53" ht="33" customHeight="1" spans="1:10">
-      <c r="A53" s="115"/>
-      <c r="B53" s="116"/>
-      <c r="C53" s="116"/>
-      <c r="D53" s="111" t="s">
+      <c r="A53" s="108"/>
+      <c r="B53" s="109"/>
+      <c r="C53" s="109"/>
+      <c r="D53" s="105" t="s">
         <v>161</v>
       </c>
-      <c r="E53" s="112"/>
-      <c r="F53" s="112"/>
-      <c r="G53" s="113" t="s">
+      <c r="E53" s="106"/>
+      <c r="F53" s="106"/>
+      <c r="G53" s="107" t="s">
         <v>162</v>
       </c>
-      <c r="H53" s="114"/>
-      <c r="I53" s="181"/>
-      <c r="J53" s="179"/>
+      <c r="H53" s="107"/>
+      <c r="I53" s="169"/>
+      <c r="J53" s="167"/>
     </row>
     <row r="54" ht="33" customHeight="1" spans="1:10">
-      <c r="A54" s="117"/>
-      <c r="B54" s="118"/>
-      <c r="C54" s="118"/>
-      <c r="D54" s="117"/>
-      <c r="E54" s="118"/>
-      <c r="F54" s="119"/>
-      <c r="G54" s="120" t="s">
+      <c r="A54" s="110"/>
+      <c r="B54" s="111"/>
+      <c r="C54" s="111"/>
+      <c r="D54" s="110"/>
+      <c r="E54" s="111"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="111" t="s">
         <v>163</v>
       </c>
-      <c r="H54" s="118"/>
-      <c r="I54" s="182"/>
-      <c r="J54" s="121"/>
+      <c r="H54" s="111"/>
+      <c r="I54" s="170"/>
+      <c r="J54" s="113"/>
     </row>
     <row r="55" ht="21.75" customHeight="1" spans="1:10">
-      <c r="A55" s="121"/>
-      <c r="B55" s="122" t="str">
+      <c r="A55" s="113"/>
+      <c r="B55" s="114" t="str">
         <f>IF(AND(3&lt;$I$21,$I$21&lt;=26.9),$A$37,IF(AND(26.9&lt;$I$21,$I$21&lt;=41.9),$A$38,IF(AND(41.9&lt;$I$21,$I$21&lt;=53.9),CONCATENATE("2","*",$A$37))))</f>
         <v>BCAH-96-410-XEF </v>
       </c>
-      <c r="C55" s="121"/>
-      <c r="D55" s="121"/>
-      <c r="E55" s="121"/>
-      <c r="F55" s="121"/>
-      <c r="G55" s="121"/>
-      <c r="H55" s="123"/>
-      <c r="I55" s="123"/>
-      <c r="J55" s="123"/>
+      <c r="C55" s="113"/>
+      <c r="D55" s="113"/>
+      <c r="E55" s="113"/>
+      <c r="F55" s="113"/>
+      <c r="G55" s="113"/>
+      <c r="H55" s="114"/>
+      <c r="I55" s="114"/>
+      <c r="J55" s="114"/>
     </row>
     <row r="56" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:10">
-      <c r="A56" s="121"/>
-      <c r="B56" s="123"/>
-      <c r="C56" s="121"/>
-      <c r="D56" s="121"/>
-      <c r="E56" s="121"/>
-      <c r="F56" s="121"/>
-      <c r="G56" s="121"/>
-      <c r="H56" s="123"/>
-      <c r="I56" s="123"/>
-      <c r="J56" s="123"/>
+      <c r="A56" s="113"/>
+      <c r="B56" s="114"/>
+      <c r="C56" s="113"/>
+      <c r="D56" s="113"/>
+      <c r="E56" s="113"/>
+      <c r="F56" s="113"/>
+      <c r="G56" s="113"/>
+      <c r="H56" s="114"/>
+      <c r="I56" s="114"/>
+      <c r="J56" s="114"/>
     </row>
     <row r="57" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:10">
-      <c r="A57" s="121"/>
-      <c r="B57" s="123"/>
-      <c r="C57" s="121"/>
-      <c r="D57" s="121"/>
-      <c r="E57" s="121"/>
-      <c r="F57" s="121"/>
-      <c r="G57" s="121"/>
-      <c r="H57" s="123"/>
-      <c r="I57" s="123"/>
-      <c r="J57" s="123"/>
+      <c r="A57" s="113"/>
+      <c r="B57" s="114"/>
+      <c r="C57" s="113"/>
+      <c r="D57" s="113"/>
+      <c r="E57" s="113"/>
+      <c r="F57" s="113"/>
+      <c r="G57" s="113"/>
+      <c r="H57" s="114"/>
+      <c r="I57" s="114"/>
+      <c r="J57" s="114"/>
     </row>
     <row r="58" ht="29.4" customHeight="1" spans="1:10">
-      <c r="A58" s="121"/>
-      <c r="B58" s="121"/>
-      <c r="C58" s="121"/>
-      <c r="D58" s="121"/>
-      <c r="E58" s="121"/>
-      <c r="F58" s="121"/>
-      <c r="G58" s="121"/>
-      <c r="H58" s="123"/>
-      <c r="I58" s="123"/>
-      <c r="J58" s="123"/>
+      <c r="A58" s="113"/>
+      <c r="B58" s="113"/>
+      <c r="C58" s="113"/>
+      <c r="D58" s="113"/>
+      <c r="E58" s="113"/>
+      <c r="F58" s="113"/>
+      <c r="G58" s="113"/>
+      <c r="H58" s="114"/>
+      <c r="I58" s="114"/>
+      <c r="J58" s="114"/>
     </row>
     <row r="59" ht="32.25" customHeight="1" spans="1:10">
-      <c r="A59" s="124" t="s">
+      <c r="A59" s="115" t="s">
         <v>164</v>
       </c>
-      <c r="B59" s="124"/>
-      <c r="C59" s="124"/>
-      <c r="D59" s="124"/>
-      <c r="E59" s="124"/>
-      <c r="F59" s="125" t="s">
+      <c r="B59" s="115"/>
+      <c r="C59" s="115"/>
+      <c r="D59" s="115"/>
+      <c r="E59" s="115"/>
+      <c r="F59" s="116" t="s">
         <v>165</v>
       </c>
-      <c r="G59" s="125"/>
-      <c r="H59" s="125"/>
-      <c r="I59" s="125"/>
-      <c r="J59" s="125"/>
+      <c r="G59" s="116"/>
+      <c r="H59" s="116"/>
+      <c r="I59" s="116"/>
+      <c r="J59" s="116"/>
     </row>
     <row r="60" ht="50.25" customHeight="1" spans="1:10">
-      <c r="A60" s="126" t="s">
+      <c r="A60" s="117" t="s">
         <v>166</v>
       </c>
-      <c r="B60" s="127" t="s">
+      <c r="B60" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="C60" s="128" t="s">
+      <c r="C60" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="D60" s="129">
+      <c r="D60" s="120">
         <v>30</v>
       </c>
-      <c r="E60" s="126" t="s">
+      <c r="E60" s="117" t="s">
         <v>69</v>
       </c>
-      <c r="F60" s="130" t="s">
+      <c r="F60" s="121" t="s">
         <v>169</v>
       </c>
-      <c r="G60" s="131" t="s">
+      <c r="G60" s="122" t="s">
         <v>170</v>
       </c>
-      <c r="H60" s="130" t="s">
+      <c r="H60" s="121" t="s">
         <v>171</v>
       </c>
-      <c r="I60" s="183">
+      <c r="I60" s="121">
         <v>10</v>
       </c>
-      <c r="J60" s="130" t="s">
+      <c r="J60" s="121" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="61" ht="47.25" customHeight="1" spans="1:10">
-      <c r="A61" s="132" t="s">
+      <c r="A61" s="123" t="s">
         <v>173</v>
       </c>
-      <c r="B61" s="132"/>
-      <c r="C61" s="132"/>
-      <c r="D61" s="132"/>
-      <c r="E61" s="133"/>
-      <c r="F61" s="134" t="s">
+      <c r="B61" s="123"/>
+      <c r="C61" s="123"/>
+      <c r="D61" s="123"/>
+      <c r="E61" s="124"/>
+      <c r="F61" s="125" t="s">
         <v>174</v>
       </c>
-      <c r="G61" s="135" t="s">
+      <c r="G61" s="126" t="s">
         <v>175</v>
       </c>
-      <c r="H61" s="134" t="s">
+      <c r="H61" s="125" t="s">
         <v>117</v>
       </c>
-      <c r="I61" s="184">
+      <c r="I61" s="171">
         <f>I27</f>
-        <v>705.702433333333</v>
-      </c>
-      <c r="J61" s="134" t="s">
+        <v>1158.78888888889</v>
+      </c>
+      <c r="J61" s="125" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="62" ht="46.5" customHeight="1" spans="1:10">
-      <c r="A62" s="136" t="s">
+      <c r="A62" s="127" t="s">
         <v>176</v>
       </c>
-      <c r="B62" s="137" t="s">
+      <c r="B62" s="128" t="s">
         <v>177</v>
       </c>
-      <c r="C62" s="136" t="s">
+      <c r="C62" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="D62" s="138">
+      <c r="D62" s="127">
         <f>D8</f>
+        <v>12</v>
+      </c>
+      <c r="E62" s="129" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62" s="121" t="s">
+        <v>178</v>
+      </c>
+      <c r="G62" s="122" t="s">
+        <v>179</v>
+      </c>
+      <c r="H62" s="121" t="s">
+        <v>180</v>
+      </c>
+      <c r="I62" s="172">
+        <f>D60-I21</f>
+        <v>9.28000100501789</v>
+      </c>
+      <c r="J62" s="121" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="63" ht="46.5" customHeight="1" spans="1:10">
+      <c r="A63" s="130"/>
+      <c r="B63" s="122" t="s">
+        <v>181</v>
+      </c>
+      <c r="C63" s="121" t="s">
+        <v>182</v>
+      </c>
+      <c r="D63" s="131" t="s">
+        <v>183</v>
+      </c>
+      <c r="E63" s="132"/>
+      <c r="F63" s="125" t="s">
+        <v>184</v>
+      </c>
+      <c r="G63" s="126" t="s">
+        <v>185</v>
+      </c>
+      <c r="H63" s="125" t="s">
+        <v>186</v>
+      </c>
+      <c r="I63" s="171">
+        <f>I61/(I62*I60)</f>
+        <v>12.4869478813882</v>
+      </c>
+      <c r="J63" s="125" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="64" ht="36" customHeight="1" spans="1:15">
+      <c r="A64" s="133"/>
+      <c r="B64" s="128" t="s">
+        <v>187</v>
+      </c>
+      <c r="C64" s="134"/>
+      <c r="D64" s="135"/>
+      <c r="E64" s="135"/>
+      <c r="F64" s="116" t="s">
+        <v>188</v>
+      </c>
+      <c r="G64" s="116"/>
+      <c r="H64" s="116"/>
+      <c r="I64" s="116"/>
+      <c r="J64" s="116"/>
+      <c r="K64" s="116" t="s">
+        <v>189</v>
+      </c>
+      <c r="L64" s="116"/>
+      <c r="M64" s="116"/>
+      <c r="N64" s="116"/>
+      <c r="O64" s="116"/>
+    </row>
+    <row r="65" ht="36" customHeight="1" spans="1:15">
+      <c r="A65" s="175"/>
+      <c r="B65" s="122" t="s">
+        <v>190</v>
+      </c>
+      <c r="C65" s="176"/>
+      <c r="D65" s="177"/>
+      <c r="E65" s="177"/>
+      <c r="F65" s="178" t="s">
+        <v>191</v>
+      </c>
+      <c r="G65" s="179" t="s">
+        <v>192</v>
+      </c>
+      <c r="H65" s="179" t="s">
+        <v>193</v>
+      </c>
+      <c r="I65" s="179">
+        <v>7330</v>
+      </c>
+      <c r="J65" s="179" t="s">
+        <v>194</v>
+      </c>
+      <c r="K65" s="194" t="s">
+        <v>195</v>
+      </c>
+      <c r="L65" s="179" t="s">
+        <v>192</v>
+      </c>
+      <c r="M65" s="179" t="s">
+        <v>196</v>
+      </c>
+      <c r="N65" s="179">
+        <v>13</v>
+      </c>
+      <c r="O65" s="179" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" ht="34.5" customHeight="1" spans="1:15">
+      <c r="A66" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="B66" s="180" t="s">
+        <v>198</v>
+      </c>
+      <c r="C66" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="D66" s="181">
+        <f>I21/D63</f>
+        <v>5.17999974874553</v>
+      </c>
+      <c r="E66" s="132" t="s">
+        <v>69</v>
+      </c>
+      <c r="F66" s="178"/>
+      <c r="G66" s="182" t="s">
+        <v>200</v>
+      </c>
+      <c r="H66" s="183" t="s">
+        <v>193</v>
+      </c>
+      <c r="I66" s="183">
+        <v>6963</v>
+      </c>
+      <c r="J66" s="183" t="s">
+        <v>194</v>
+      </c>
+      <c r="K66" s="194"/>
+      <c r="L66" s="182" t="s">
+        <v>200</v>
+      </c>
+      <c r="M66" s="183" t="s">
+        <v>196</v>
+      </c>
+      <c r="N66" s="183">
+        <v>18</v>
+      </c>
+      <c r="O66" s="183" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" ht="34.5" customHeight="1" spans="1:15">
+      <c r="A67" s="184" t="s">
+        <v>201</v>
+      </c>
+      <c r="B67" s="185" t="s">
+        <v>202</v>
+      </c>
+      <c r="C67" s="184" t="s">
+        <v>203</v>
+      </c>
+      <c r="D67" s="186">
+        <f>D66*24</f>
+        <v>124.319993969893</v>
+      </c>
+      <c r="E67" s="129" t="s">
+        <v>204</v>
+      </c>
+      <c r="F67" s="178"/>
+      <c r="G67" s="179" t="s">
+        <v>205</v>
+      </c>
+      <c r="H67" s="179" t="s">
+        <v>193</v>
+      </c>
+      <c r="I67" s="179">
+        <v>8050</v>
+      </c>
+      <c r="J67" s="179" t="s">
+        <v>194</v>
+      </c>
+      <c r="K67" s="194"/>
+      <c r="L67" s="179" t="s">
+        <v>205</v>
+      </c>
+      <c r="M67" s="179" t="s">
+        <v>196</v>
+      </c>
+      <c r="N67" s="179">
+        <v>18</v>
+      </c>
+      <c r="O67" s="179" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" ht="34.5" customHeight="1" spans="1:15">
+      <c r="A68" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="B68" s="187" t="s">
+        <v>207</v>
+      </c>
+      <c r="C68" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D68" s="188">
+        <f>D67*30*0.7</f>
+        <v>2610.71987336775</v>
+      </c>
+      <c r="E68" s="132" t="s">
+        <v>209</v>
+      </c>
+      <c r="F68" s="178"/>
+      <c r="G68" s="182" t="s">
+        <v>210</v>
+      </c>
+      <c r="H68" s="183" t="s">
+        <v>193</v>
+      </c>
+      <c r="I68" s="183">
+        <v>8512</v>
+      </c>
+      <c r="J68" s="183" t="s">
+        <v>194</v>
+      </c>
+      <c r="K68" s="194"/>
+      <c r="L68" s="182" t="s">
+        <v>210</v>
+      </c>
+      <c r="M68" s="183" t="s">
+        <v>196</v>
+      </c>
+      <c r="N68" s="183">
+        <v>22</v>
+      </c>
+      <c r="O68" s="183" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" ht="34.5" customHeight="1" spans="1:15">
+      <c r="A69" s="184" t="s">
+        <v>211</v>
+      </c>
+      <c r="B69" s="185" t="s">
+        <v>212</v>
+      </c>
+      <c r="C69" s="184" t="s">
+        <v>213</v>
+      </c>
+      <c r="D69" s="127">
+        <v>700</v>
+      </c>
+      <c r="E69" s="129" t="s">
+        <v>214</v>
+      </c>
+      <c r="F69" s="178"/>
+      <c r="G69" s="179" t="s">
+        <v>215</v>
+      </c>
+      <c r="H69" s="179" t="s">
+        <v>193</v>
+      </c>
+      <c r="I69" s="179">
+        <v>8200</v>
+      </c>
+      <c r="J69" s="179" t="s">
+        <v>194</v>
+      </c>
+      <c r="K69" s="194"/>
+      <c r="L69" s="179" t="s">
+        <v>215</v>
+      </c>
+      <c r="M69" s="179" t="s">
+        <v>196</v>
+      </c>
+      <c r="N69" s="179">
+        <v>18</v>
+      </c>
+      <c r="O69" s="179" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" ht="34.5" customHeight="1" spans="1:15">
+      <c r="A70" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="B70" s="187" t="s">
+        <v>216</v>
+      </c>
+      <c r="C70" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="D70" s="189">
+        <f>D68*D69</f>
+        <v>1827503.91135742</v>
+      </c>
+      <c r="E70" s="132"/>
+      <c r="F70" s="190" t="s">
+        <v>218</v>
+      </c>
+      <c r="G70" s="182" t="s">
+        <v>192</v>
+      </c>
+      <c r="H70" s="183" t="s">
+        <v>219</v>
+      </c>
+      <c r="I70" s="183">
+        <v>7696</v>
+      </c>
+      <c r="J70" s="183" t="s">
+        <v>194</v>
+      </c>
+      <c r="K70" s="195" t="s">
+        <v>220</v>
+      </c>
+      <c r="L70" s="182" t="s">
+        <v>192</v>
+      </c>
+      <c r="M70" s="183" t="s">
+        <v>221</v>
+      </c>
+      <c r="N70" s="183">
+        <v>15</v>
+      </c>
+      <c r="O70" s="183" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" ht="29.25" customHeight="1" spans="6:15">
+      <c r="F71" s="190"/>
+      <c r="G71" s="191" t="s">
+        <v>200</v>
+      </c>
+      <c r="H71" s="191" t="s">
+        <v>219</v>
+      </c>
+      <c r="I71" s="191">
+        <v>7310</v>
+      </c>
+      <c r="J71" s="191" t="s">
+        <v>194</v>
+      </c>
+      <c r="K71" s="195"/>
+      <c r="L71" s="191" t="s">
+        <v>200</v>
+      </c>
+      <c r="M71" s="191" t="s">
+        <v>221</v>
+      </c>
+      <c r="N71" s="191">
+        <v>20</v>
+      </c>
+      <c r="O71" s="191" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" ht="29.25" customHeight="1" spans="6:15">
+      <c r="F72" s="190"/>
+      <c r="G72" s="182" t="s">
+        <v>205</v>
+      </c>
+      <c r="H72" s="183" t="s">
+        <v>219</v>
+      </c>
+      <c r="I72" s="183">
+        <v>8288</v>
+      </c>
+      <c r="J72" s="183" t="s">
+        <v>194</v>
+      </c>
+      <c r="K72" s="195"/>
+      <c r="L72" s="182" t="s">
+        <v>205</v>
+      </c>
+      <c r="M72" s="183" t="s">
+        <v>221</v>
+      </c>
+      <c r="N72" s="183">
+        <v>20</v>
+      </c>
+      <c r="O72" s="183" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" ht="29.25" customHeight="1" spans="6:15">
+      <c r="F73" s="190"/>
+      <c r="G73" s="191" t="s">
+        <v>210</v>
+      </c>
+      <c r="H73" s="191" t="s">
+        <v>219</v>
+      </c>
+      <c r="I73" s="191">
+        <v>8736</v>
+      </c>
+      <c r="J73" s="191" t="s">
+        <v>194</v>
+      </c>
+      <c r="K73" s="195"/>
+      <c r="L73" s="191" t="s">
+        <v>210</v>
+      </c>
+      <c r="M73" s="191" t="s">
+        <v>221</v>
+      </c>
+      <c r="N73" s="191">
+        <v>24</v>
+      </c>
+      <c r="O73" s="191" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="74" ht="29.25" customHeight="1" spans="6:15">
+      <c r="F74" s="190"/>
+      <c r="G74" s="182" t="s">
+        <v>215</v>
+      </c>
+      <c r="H74" s="183" t="s">
+        <v>219</v>
+      </c>
+      <c r="I74" s="183">
+        <v>8400</v>
+      </c>
+      <c r="J74" s="183" t="s">
+        <v>194</v>
+      </c>
+      <c r="K74" s="195"/>
+      <c r="L74" s="182" t="s">
+        <v>215</v>
+      </c>
+      <c r="M74" s="183" t="s">
+        <v>221</v>
+      </c>
+      <c r="N74" s="183">
+        <v>20</v>
+      </c>
+      <c r="O74" s="183" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1" spans="6:15">
+      <c r="F75" s="192" t="s">
+        <v>222</v>
+      </c>
+      <c r="G75" s="193" t="s">
+        <v>192</v>
+      </c>
+      <c r="H75" s="193" t="s">
+        <v>223</v>
+      </c>
+      <c r="I75" s="193">
+        <v>8050</v>
+      </c>
+      <c r="J75" s="193" t="s">
+        <v>194</v>
+      </c>
+      <c r="K75" s="196" t="s">
+        <v>224</v>
+      </c>
+      <c r="L75" s="193" t="s">
+        <v>192</v>
+      </c>
+      <c r="M75" s="193" t="s">
+        <v>225</v>
+      </c>
+      <c r="N75" s="193">
+        <v>17</v>
+      </c>
+      <c r="O75" s="193" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1" spans="6:15">
+      <c r="F76" s="192"/>
+      <c r="G76" s="182" t="s">
+        <v>200</v>
+      </c>
+      <c r="H76" s="183" t="s">
+        <v>223</v>
+      </c>
+      <c r="I76" s="183">
+        <v>7676</v>
+      </c>
+      <c r="J76" s="183" t="s">
+        <v>194</v>
+      </c>
+      <c r="K76" s="196"/>
+      <c r="L76" s="182" t="s">
+        <v>200</v>
+      </c>
+      <c r="M76" s="183" t="s">
+        <v>225</v>
+      </c>
+      <c r="N76" s="183">
+        <v>22</v>
+      </c>
+      <c r="O76" s="183" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1" spans="6:15">
+      <c r="F77" s="192"/>
+      <c r="G77" s="193" t="s">
+        <v>205</v>
+      </c>
+      <c r="H77" s="193" t="s">
+        <v>223</v>
+      </c>
+      <c r="I77" s="193">
+        <v>8624</v>
+      </c>
+      <c r="J77" s="193" t="s">
+        <v>194</v>
+      </c>
+      <c r="K77" s="196"/>
+      <c r="L77" s="193" t="s">
+        <v>205</v>
+      </c>
+      <c r="M77" s="193" t="s">
+        <v>225</v>
+      </c>
+      <c r="N77" s="193">
+        <v>22</v>
+      </c>
+      <c r="O77" s="193" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1" spans="6:15">
+      <c r="F78" s="192"/>
+      <c r="G78" s="182" t="s">
+        <v>210</v>
+      </c>
+      <c r="H78" s="183" t="s">
+        <v>223</v>
+      </c>
+      <c r="I78" s="183">
+        <v>8960</v>
+      </c>
+      <c r="J78" s="183" t="s">
+        <v>194</v>
+      </c>
+      <c r="K78" s="196"/>
+      <c r="L78" s="182" t="s">
+        <v>210</v>
+      </c>
+      <c r="M78" s="183" t="s">
+        <v>225</v>
+      </c>
+      <c r="N78" s="183">
+        <v>26</v>
+      </c>
+      <c r="O78" s="183" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1" spans="6:15">
+      <c r="F79" s="192"/>
+      <c r="G79" s="193" t="s">
+        <v>215</v>
+      </c>
+      <c r="H79" s="193" t="s">
+        <v>223</v>
+      </c>
+      <c r="I79" s="193">
+        <v>8680</v>
+      </c>
+      <c r="J79" s="193" t="s">
+        <v>194</v>
+      </c>
+      <c r="K79" s="196"/>
+      <c r="L79" s="193" t="s">
+        <v>215</v>
+      </c>
+      <c r="M79" s="193" t="s">
+        <v>225</v>
+      </c>
+      <c r="N79" s="193">
+        <v>22</v>
+      </c>
+      <c r="O79" s="193" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="80" ht="36.75" customHeight="1" spans="6:10">
+      <c r="F80" s="116" t="s">
+        <v>226</v>
+      </c>
+      <c r="G80" s="116"/>
+      <c r="H80" s="116"/>
+      <c r="I80" s="116"/>
+      <c r="J80" s="116"/>
+    </row>
+    <row r="81" ht="27" customHeight="1" spans="6:10">
+      <c r="F81" s="178" t="s">
+        <v>195</v>
+      </c>
+      <c r="G81" s="179" t="s">
+        <v>192</v>
+      </c>
+      <c r="H81" s="179" t="s">
+        <v>227</v>
+      </c>
+      <c r="I81" s="179">
         <v>10</v>
       </c>
-      <c r="E62" s="139" t="s">
-        <v>27</v>
-      </c>
-      <c r="F62" s="130" t="s">
-        <v>178</v>
-      </c>
-      <c r="G62" s="131" t="s">
-        <v>179</v>
-      </c>
-      <c r="H62" s="130" t="s">
-        <v>180</v>
-      </c>
-      <c r="I62" s="185">
-        <f>D60-I21</f>
-        <v>14.9688438566863</v>
-      </c>
-      <c r="J62" s="130" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="63" ht="46.5" customHeight="1" spans="1:10">
-      <c r="A63" s="140"/>
-      <c r="B63" s="131" t="s">
-        <v>181</v>
-      </c>
-      <c r="C63" s="130" t="s">
-        <v>182</v>
-      </c>
-      <c r="D63" s="141">
-        <v>5</v>
-      </c>
-      <c r="E63" s="142"/>
-      <c r="F63" s="134" t="s">
-        <v>183</v>
-      </c>
-      <c r="G63" s="135" t="s">
-        <v>184</v>
-      </c>
-      <c r="H63" s="134" t="s">
-        <v>185</v>
-      </c>
-      <c r="I63" s="184">
-        <f>I61/(I62*I60)</f>
-        <v>4.71447521324841</v>
-      </c>
-      <c r="J63" s="134" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="64" ht="36" customHeight="1" spans="1:15">
-      <c r="A64" s="143"/>
-      <c r="B64" s="137" t="s">
-        <v>186</v>
-      </c>
-      <c r="C64" s="144"/>
-      <c r="D64" s="145"/>
-      <c r="E64" s="145"/>
-      <c r="F64" s="125" t="s">
-        <v>187</v>
-      </c>
-      <c r="G64" s="125"/>
-      <c r="H64" s="125"/>
-      <c r="I64" s="125"/>
-      <c r="J64" s="125"/>
-      <c r="K64" s="125" t="s">
-        <v>188</v>
-      </c>
-      <c r="L64" s="125"/>
-      <c r="M64" s="125"/>
-      <c r="N64" s="125"/>
-      <c r="O64" s="125"/>
-    </row>
-    <row r="65" ht="36" customHeight="1" spans="1:15">
-      <c r="A65" s="189"/>
-      <c r="B65" s="131" t="s">
-        <v>189</v>
-      </c>
-      <c r="C65" s="190"/>
-      <c r="D65" s="191"/>
-      <c r="E65" s="191"/>
-      <c r="F65" s="192" t="s">
-        <v>190</v>
-      </c>
-      <c r="G65" s="193" t="s">
-        <v>191</v>
-      </c>
-      <c r="H65" s="193" t="s">
+      <c r="J81" s="179" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="82" ht="27" customHeight="1" spans="6:10">
+      <c r="F82" s="178"/>
+      <c r="G82" s="182" t="s">
+        <v>200</v>
+      </c>
+      <c r="H82" s="183" t="s">
+        <v>227</v>
+      </c>
+      <c r="I82" s="183">
+        <v>15</v>
+      </c>
+      <c r="J82" s="183" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="83" ht="27" customHeight="1" spans="6:10">
+      <c r="F83" s="178"/>
+      <c r="G83" s="179" t="s">
+        <v>205</v>
+      </c>
+      <c r="H83" s="179" t="s">
+        <v>227</v>
+      </c>
+      <c r="I83" s="179">
+        <v>15</v>
+      </c>
+      <c r="J83" s="179" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="84" ht="27" customHeight="1" spans="6:10">
+      <c r="F84" s="178"/>
+      <c r="G84" s="182" t="s">
+        <v>210</v>
+      </c>
+      <c r="H84" s="183" t="s">
+        <v>227</v>
+      </c>
+      <c r="I84" s="183">
+        <v>20</v>
+      </c>
+      <c r="J84" s="183" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="85" ht="27" customHeight="1" spans="6:10">
+      <c r="F85" s="178"/>
+      <c r="G85" s="179" t="s">
+        <v>215</v>
+      </c>
+      <c r="H85" s="179" t="s">
+        <v>227</v>
+      </c>
+      <c r="I85" s="179">
+        <v>20</v>
+      </c>
+      <c r="J85" s="179" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="86" ht="27" customHeight="1" spans="6:10">
+      <c r="F86" s="190" t="s">
+        <v>220</v>
+      </c>
+      <c r="G86" s="182" t="s">
         <v>192</v>
       </c>
-      <c r="I65" s="193">
-        <v>7330</v>
-      </c>
-      <c r="J65" s="193" t="s">
-        <v>193</v>
-      </c>
-      <c r="K65" s="209" t="s">
-        <v>194</v>
-      </c>
-      <c r="L65" s="193" t="s">
-        <v>191</v>
-      </c>
-      <c r="M65" s="193" t="s">
-        <v>195</v>
-      </c>
-      <c r="N65" s="193">
-        <v>13</v>
-      </c>
-      <c r="O65" s="193" t="s">
+      <c r="H86" s="183" t="s">
+        <v>228</v>
+      </c>
+      <c r="I86" s="183">
+        <v>12</v>
+      </c>
+      <c r="J86" s="183" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="66" ht="34.5" customHeight="1" spans="1:15">
-      <c r="A66" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="B66" s="194" t="s">
-        <v>197</v>
-      </c>
-      <c r="C66" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="D66" s="195">
-        <f>I21/D63</f>
-        <v>3.00623122866274</v>
-      </c>
-      <c r="E66" s="196" t="s">
-        <v>69</v>
-      </c>
-      <c r="F66" s="192"/>
-      <c r="G66" s="197" t="s">
-        <v>199</v>
-      </c>
-      <c r="H66" s="198" t="s">
+    <row r="87" ht="27" customHeight="1" spans="6:10">
+      <c r="F87" s="190"/>
+      <c r="G87" s="191" t="s">
+        <v>200</v>
+      </c>
+      <c r="H87" s="191" t="s">
+        <v>228</v>
+      </c>
+      <c r="I87" s="191">
+        <v>15</v>
+      </c>
+      <c r="J87" s="191" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="88" ht="27" customHeight="1" spans="6:10">
+      <c r="F88" s="190"/>
+      <c r="G88" s="182" t="s">
+        <v>205</v>
+      </c>
+      <c r="H88" s="183" t="s">
+        <v>228</v>
+      </c>
+      <c r="I88" s="183">
+        <v>15</v>
+      </c>
+      <c r="J88" s="183" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="89" ht="27" customHeight="1" spans="6:10">
+      <c r="F89" s="190"/>
+      <c r="G89" s="191" t="s">
+        <v>210</v>
+      </c>
+      <c r="H89" s="191" t="s">
+        <v>228</v>
+      </c>
+      <c r="I89" s="191">
+        <v>20</v>
+      </c>
+      <c r="J89" s="191" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="90" ht="27" customHeight="1" spans="6:10">
+      <c r="F90" s="190"/>
+      <c r="G90" s="182" t="s">
+        <v>215</v>
+      </c>
+      <c r="H90" s="183" t="s">
+        <v>228</v>
+      </c>
+      <c r="I90" s="183">
+        <v>20</v>
+      </c>
+      <c r="J90" s="183" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="91" ht="27" customHeight="1" spans="6:10">
+      <c r="F91" s="192" t="s">
+        <v>224</v>
+      </c>
+      <c r="G91" s="193" t="s">
         <v>192</v>
       </c>
-      <c r="I66" s="210">
-        <v>6963</v>
-      </c>
-      <c r="J66" s="198" t="s">
-        <v>193</v>
-      </c>
-      <c r="K66" s="209"/>
-      <c r="L66" s="197" t="s">
-        <v>199</v>
-      </c>
-      <c r="M66" s="198" t="s">
-        <v>195</v>
-      </c>
-      <c r="N66" s="210">
-        <v>18</v>
-      </c>
-      <c r="O66" s="198" t="s">
+      <c r="H91" s="193" t="s">
+        <v>229</v>
+      </c>
+      <c r="I91" s="193">
+        <v>14</v>
+      </c>
+      <c r="J91" s="193" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="67" ht="34.5" customHeight="1" spans="1:15">
-      <c r="A67" s="199" t="s">
+    <row r="92" ht="27" customHeight="1" spans="6:10">
+      <c r="F92" s="192"/>
+      <c r="G92" s="182" t="s">
         <v>200</v>
       </c>
-      <c r="B67" s="200" t="s">
-        <v>201</v>
-      </c>
-      <c r="C67" s="199" t="s">
-        <v>202</v>
-      </c>
-      <c r="D67" s="201">
-        <f>D66*24</f>
-        <v>72.1495494879057</v>
-      </c>
-      <c r="E67" s="139" t="s">
-        <v>203</v>
-      </c>
-      <c r="F67" s="192"/>
-      <c r="G67" s="193" t="s">
-        <v>204</v>
-      </c>
-      <c r="H67" s="193" t="s">
-        <v>192</v>
-      </c>
-      <c r="I67" s="193">
-        <v>8050</v>
-      </c>
-      <c r="J67" s="193" t="s">
-        <v>193</v>
-      </c>
-      <c r="K67" s="209"/>
-      <c r="L67" s="193" t="s">
-        <v>204</v>
-      </c>
-      <c r="M67" s="193" t="s">
-        <v>195</v>
-      </c>
-      <c r="N67" s="193">
-        <v>18</v>
-      </c>
-      <c r="O67" s="193" t="s">
+      <c r="H92" s="183" t="s">
+        <v>229</v>
+      </c>
+      <c r="I92" s="183">
+        <v>19</v>
+      </c>
+      <c r="J92" s="183" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="68" ht="34.5" customHeight="1" spans="1:15">
-      <c r="A68" s="43" t="s">
+    <row r="93" ht="27" customHeight="1" spans="6:10">
+      <c r="F93" s="192"/>
+      <c r="G93" s="193" t="s">
         <v>205</v>
       </c>
-      <c r="B68" s="202" t="s">
-        <v>206</v>
-      </c>
-      <c r="C68" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="D68" s="203">
-        <f>D67*30*0.7</f>
-        <v>1515.14053924602</v>
-      </c>
-      <c r="E68" s="196" t="s">
-        <v>208</v>
-      </c>
-      <c r="F68" s="192"/>
-      <c r="G68" s="197" t="s">
-        <v>209</v>
-      </c>
-      <c r="H68" s="198" t="s">
-        <v>192</v>
-      </c>
-      <c r="I68" s="210">
-        <v>8512</v>
-      </c>
-      <c r="J68" s="198" t="s">
-        <v>193</v>
-      </c>
-      <c r="K68" s="209"/>
-      <c r="L68" s="197" t="s">
-        <v>209</v>
-      </c>
-      <c r="M68" s="198" t="s">
-        <v>195</v>
-      </c>
-      <c r="N68" s="210">
-        <v>22</v>
-      </c>
-      <c r="O68" s="198" t="s">
+      <c r="H93" s="193" t="s">
+        <v>229</v>
+      </c>
+      <c r="I93" s="193">
+        <v>19</v>
+      </c>
+      <c r="J93" s="193" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="69" ht="34.5" customHeight="1" spans="1:15">
-      <c r="A69" s="199" t="s">
+    <row r="94" ht="27" customHeight="1" spans="6:10">
+      <c r="F94" s="192"/>
+      <c r="G94" s="182" t="s">
         <v>210</v>
       </c>
-      <c r="B69" s="200" t="s">
-        <v>211</v>
-      </c>
-      <c r="C69" s="199" t="s">
-        <v>212</v>
-      </c>
-      <c r="D69" s="138">
-        <v>700</v>
-      </c>
-      <c r="E69" s="139" t="s">
-        <v>213</v>
-      </c>
-      <c r="F69" s="192"/>
-      <c r="G69" s="193" t="s">
-        <v>214</v>
-      </c>
-      <c r="H69" s="193" t="s">
-        <v>192</v>
-      </c>
-      <c r="I69" s="193">
-        <v>8200</v>
-      </c>
-      <c r="J69" s="193" t="s">
-        <v>193</v>
-      </c>
-      <c r="K69" s="209"/>
-      <c r="L69" s="193" t="s">
-        <v>214</v>
-      </c>
-      <c r="M69" s="193" t="s">
-        <v>195</v>
-      </c>
-      <c r="N69" s="193">
-        <v>18</v>
-      </c>
-      <c r="O69" s="193" t="s">
+      <c r="H94" s="183" t="s">
+        <v>229</v>
+      </c>
+      <c r="I94" s="183">
+        <v>19</v>
+      </c>
+      <c r="J94" s="183" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="70" ht="34.5" customHeight="1" spans="1:15">
-      <c r="A70" s="43" t="s">
+    <row r="95" ht="27" customHeight="1" spans="6:10">
+      <c r="F95" s="192"/>
+      <c r="G95" s="193" t="s">
         <v>215</v>
       </c>
-      <c r="B70" s="202" t="s">
-        <v>215</v>
-      </c>
-      <c r="C70" s="43" t="s">
-        <v>216</v>
-      </c>
-      <c r="D70" s="204">
-        <f>D68*D69</f>
-        <v>1060598.37747221</v>
-      </c>
-      <c r="E70" s="142"/>
-      <c r="F70" s="205" t="s">
-        <v>217</v>
-      </c>
-      <c r="G70" s="197" t="s">
-        <v>191</v>
-      </c>
-      <c r="H70" s="198" t="s">
-        <v>218</v>
-      </c>
-      <c r="I70" s="210">
-        <v>7696</v>
-      </c>
-      <c r="J70" s="198" t="s">
-        <v>193</v>
-      </c>
-      <c r="K70" s="211" t="s">
-        <v>219</v>
-      </c>
-      <c r="L70" s="197" t="s">
-        <v>191</v>
-      </c>
-      <c r="M70" s="198" t="s">
-        <v>220</v>
-      </c>
-      <c r="N70" s="210">
-        <v>15</v>
-      </c>
-      <c r="O70" s="198" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="71" ht="29.25" customHeight="1" spans="6:15">
-      <c r="F71" s="205"/>
-      <c r="G71" s="206" t="s">
-        <v>199</v>
-      </c>
-      <c r="H71" s="206" t="s">
-        <v>218</v>
-      </c>
-      <c r="I71" s="206">
-        <v>7310</v>
-      </c>
-      <c r="J71" s="206" t="s">
-        <v>193</v>
-      </c>
-      <c r="K71" s="211"/>
-      <c r="L71" s="206" t="s">
-        <v>199</v>
-      </c>
-      <c r="M71" s="206" t="s">
-        <v>220</v>
-      </c>
-      <c r="N71" s="206">
-        <v>20</v>
-      </c>
-      <c r="O71" s="206" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="72" ht="29.25" customHeight="1" spans="6:15">
-      <c r="F72" s="205"/>
-      <c r="G72" s="197" t="s">
-        <v>204</v>
-      </c>
-      <c r="H72" s="198" t="s">
-        <v>218</v>
-      </c>
-      <c r="I72" s="210">
-        <v>8288</v>
-      </c>
-      <c r="J72" s="198" t="s">
-        <v>193</v>
-      </c>
-      <c r="K72" s="211"/>
-      <c r="L72" s="197" t="s">
-        <v>204</v>
-      </c>
-      <c r="M72" s="198" t="s">
-        <v>220</v>
-      </c>
-      <c r="N72" s="210">
-        <v>20</v>
-      </c>
-      <c r="O72" s="198" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="73" ht="29.25" customHeight="1" spans="6:15">
-      <c r="F73" s="205"/>
-      <c r="G73" s="206" t="s">
-        <v>209</v>
-      </c>
-      <c r="H73" s="206" t="s">
-        <v>218</v>
-      </c>
-      <c r="I73" s="206">
-        <v>8736</v>
-      </c>
-      <c r="J73" s="206" t="s">
-        <v>193</v>
-      </c>
-      <c r="K73" s="211"/>
-      <c r="L73" s="206" t="s">
-        <v>209</v>
-      </c>
-      <c r="M73" s="206" t="s">
-        <v>220</v>
-      </c>
-      <c r="N73" s="206">
+      <c r="H95" s="193" t="s">
+        <v>229</v>
+      </c>
+      <c r="I95" s="193">
         <v>24</v>
       </c>
-      <c r="O73" s="206" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="74" ht="29.25" customHeight="1" spans="6:15">
-      <c r="F74" s="205"/>
-      <c r="G74" s="197" t="s">
-        <v>214</v>
-      </c>
-      <c r="H74" s="198" t="s">
-        <v>218</v>
-      </c>
-      <c r="I74" s="210">
-        <v>8400</v>
-      </c>
-      <c r="J74" s="198" t="s">
-        <v>193</v>
-      </c>
-      <c r="K74" s="211"/>
-      <c r="L74" s="197" t="s">
-        <v>214</v>
-      </c>
-      <c r="M74" s="198" t="s">
-        <v>220</v>
-      </c>
-      <c r="N74" s="210">
-        <v>20</v>
-      </c>
-      <c r="O74" s="198" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="75" ht="30" customHeight="1" spans="6:15">
-      <c r="F75" s="207" t="s">
-        <v>221</v>
-      </c>
-      <c r="G75" s="208" t="s">
-        <v>191</v>
-      </c>
-      <c r="H75" s="208" t="s">
-        <v>222</v>
-      </c>
-      <c r="I75" s="208">
-        <v>8050</v>
-      </c>
-      <c r="J75" s="208" t="s">
-        <v>193</v>
-      </c>
-      <c r="K75" s="212" t="s">
-        <v>223</v>
-      </c>
-      <c r="L75" s="208" t="s">
-        <v>191</v>
-      </c>
-      <c r="M75" s="208" t="s">
-        <v>224</v>
-      </c>
-      <c r="N75" s="208">
-        <v>17</v>
-      </c>
-      <c r="O75" s="208" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="76" ht="30" customHeight="1" spans="6:15">
-      <c r="F76" s="207"/>
-      <c r="G76" s="197" t="s">
-        <v>199</v>
-      </c>
-      <c r="H76" s="198" t="s">
-        <v>222</v>
-      </c>
-      <c r="I76" s="210">
-        <v>7676</v>
-      </c>
-      <c r="J76" s="198" t="s">
-        <v>193</v>
-      </c>
-      <c r="K76" s="212"/>
-      <c r="L76" s="197" t="s">
-        <v>199</v>
-      </c>
-      <c r="M76" s="198" t="s">
-        <v>224</v>
-      </c>
-      <c r="N76" s="210">
-        <v>22</v>
-      </c>
-      <c r="O76" s="198" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="77" ht="30" customHeight="1" spans="6:15">
-      <c r="F77" s="207"/>
-      <c r="G77" s="208" t="s">
-        <v>204</v>
-      </c>
-      <c r="H77" s="208" t="s">
-        <v>222</v>
-      </c>
-      <c r="I77" s="208">
-        <v>8624</v>
-      </c>
-      <c r="J77" s="208" t="s">
-        <v>193</v>
-      </c>
-      <c r="K77" s="212"/>
-      <c r="L77" s="208" t="s">
-        <v>204</v>
-      </c>
-      <c r="M77" s="208" t="s">
-        <v>224</v>
-      </c>
-      <c r="N77" s="208">
-        <v>22</v>
-      </c>
-      <c r="O77" s="208" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="78" ht="30" customHeight="1" spans="6:15">
-      <c r="F78" s="207"/>
-      <c r="G78" s="197" t="s">
-        <v>209</v>
-      </c>
-      <c r="H78" s="198" t="s">
-        <v>222</v>
-      </c>
-      <c r="I78" s="210">
-        <v>8960</v>
-      </c>
-      <c r="J78" s="198" t="s">
-        <v>193</v>
-      </c>
-      <c r="K78" s="212"/>
-      <c r="L78" s="197" t="s">
-        <v>209</v>
-      </c>
-      <c r="M78" s="198" t="s">
-        <v>224</v>
-      </c>
-      <c r="N78" s="210">
-        <v>26</v>
-      </c>
-      <c r="O78" s="198" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="79" ht="30" customHeight="1" spans="6:15">
-      <c r="F79" s="207"/>
-      <c r="G79" s="208" t="s">
-        <v>214</v>
-      </c>
-      <c r="H79" s="208" t="s">
-        <v>222</v>
-      </c>
-      <c r="I79" s="208">
-        <v>8680</v>
-      </c>
-      <c r="J79" s="208" t="s">
-        <v>193</v>
-      </c>
-      <c r="K79" s="212"/>
-      <c r="L79" s="208" t="s">
-        <v>214</v>
-      </c>
-      <c r="M79" s="208" t="s">
-        <v>224</v>
-      </c>
-      <c r="N79" s="208">
-        <v>22</v>
-      </c>
-      <c r="O79" s="208" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="80" ht="36.75" customHeight="1" spans="6:10">
-      <c r="F80" s="125" t="s">
-        <v>225</v>
-      </c>
-      <c r="G80" s="125"/>
-      <c r="H80" s="125"/>
-      <c r="I80" s="125"/>
-      <c r="J80" s="125"/>
-    </row>
-    <row r="81" ht="27" customHeight="1" spans="6:10">
-      <c r="F81" s="192" t="s">
-        <v>194</v>
-      </c>
-      <c r="G81" s="193" t="s">
-        <v>191</v>
-      </c>
-      <c r="H81" s="193" t="s">
-        <v>226</v>
-      </c>
-      <c r="I81" s="193">
-        <v>10</v>
-      </c>
-      <c r="J81" s="193" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="82" ht="27" customHeight="1" spans="6:10">
-      <c r="F82" s="192"/>
-      <c r="G82" s="197" t="s">
-        <v>199</v>
-      </c>
-      <c r="H82" s="198" t="s">
-        <v>226</v>
-      </c>
-      <c r="I82" s="210">
-        <v>15</v>
-      </c>
-      <c r="J82" s="198" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="83" ht="27" customHeight="1" spans="6:10">
-      <c r="F83" s="192"/>
-      <c r="G83" s="193" t="s">
-        <v>204</v>
-      </c>
-      <c r="H83" s="193" t="s">
-        <v>226</v>
-      </c>
-      <c r="I83" s="193">
-        <v>15</v>
-      </c>
-      <c r="J83" s="193" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="84" ht="27" customHeight="1" spans="6:10">
-      <c r="F84" s="192"/>
-      <c r="G84" s="197" t="s">
-        <v>209</v>
-      </c>
-      <c r="H84" s="198" t="s">
-        <v>226</v>
-      </c>
-      <c r="I84" s="210">
-        <v>20</v>
-      </c>
-      <c r="J84" s="198" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="85" ht="27" customHeight="1" spans="6:10">
-      <c r="F85" s="192"/>
-      <c r="G85" s="193" t="s">
-        <v>214</v>
-      </c>
-      <c r="H85" s="193" t="s">
-        <v>226</v>
-      </c>
-      <c r="I85" s="193">
-        <v>20</v>
-      </c>
-      <c r="J85" s="193" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="86" ht="27" customHeight="1" spans="6:10">
-      <c r="F86" s="205" t="s">
-        <v>219</v>
-      </c>
-      <c r="G86" s="197" t="s">
-        <v>191</v>
-      </c>
-      <c r="H86" s="198" t="s">
-        <v>227</v>
-      </c>
-      <c r="I86" s="210">
-        <v>12</v>
-      </c>
-      <c r="J86" s="198" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="87" ht="27" customHeight="1" spans="6:10">
-      <c r="F87" s="205"/>
-      <c r="G87" s="206" t="s">
-        <v>199</v>
-      </c>
-      <c r="H87" s="206" t="s">
-        <v>227</v>
-      </c>
-      <c r="I87" s="206">
-        <v>15</v>
-      </c>
-      <c r="J87" s="206" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="88" ht="27" customHeight="1" spans="6:10">
-      <c r="F88" s="205"/>
-      <c r="G88" s="197" t="s">
-        <v>204</v>
-      </c>
-      <c r="H88" s="198" t="s">
-        <v>227</v>
-      </c>
-      <c r="I88" s="210">
-        <v>15</v>
-      </c>
-      <c r="J88" s="198" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="89" ht="27" customHeight="1" spans="6:10">
-      <c r="F89" s="205"/>
-      <c r="G89" s="206" t="s">
-        <v>209</v>
-      </c>
-      <c r="H89" s="206" t="s">
-        <v>227</v>
-      </c>
-      <c r="I89" s="206">
-        <v>20</v>
-      </c>
-      <c r="J89" s="206" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="90" ht="27" customHeight="1" spans="6:10">
-      <c r="F90" s="205"/>
-      <c r="G90" s="197" t="s">
-        <v>214</v>
-      </c>
-      <c r="H90" s="198" t="s">
-        <v>227</v>
-      </c>
-      <c r="I90" s="210">
-        <v>20</v>
-      </c>
-      <c r="J90" s="198" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="91" ht="27" customHeight="1" spans="6:10">
-      <c r="F91" s="207" t="s">
-        <v>223</v>
-      </c>
-      <c r="G91" s="208" t="s">
-        <v>191</v>
-      </c>
-      <c r="H91" s="208" t="s">
-        <v>228</v>
-      </c>
-      <c r="I91" s="208">
-        <v>14</v>
-      </c>
-      <c r="J91" s="208" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="92" ht="27" customHeight="1" spans="6:10">
-      <c r="F92" s="207"/>
-      <c r="G92" s="197" t="s">
-        <v>199</v>
-      </c>
-      <c r="H92" s="198" t="s">
-        <v>228</v>
-      </c>
-      <c r="I92" s="210">
-        <v>19</v>
-      </c>
-      <c r="J92" s="198" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="93" ht="27" customHeight="1" spans="6:10">
-      <c r="F93" s="207"/>
-      <c r="G93" s="208" t="s">
-        <v>204</v>
-      </c>
-      <c r="H93" s="208" t="s">
-        <v>228</v>
-      </c>
-      <c r="I93" s="208">
-        <v>19</v>
-      </c>
-      <c r="J93" s="208" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="94" ht="27" customHeight="1" spans="6:10">
-      <c r="F94" s="207"/>
-      <c r="G94" s="197" t="s">
-        <v>209</v>
-      </c>
-      <c r="H94" s="198" t="s">
-        <v>228</v>
-      </c>
-      <c r="I94" s="210">
-        <v>19</v>
-      </c>
-      <c r="J94" s="198" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="95" ht="27" customHeight="1" spans="6:10">
-      <c r="F95" s="207"/>
-      <c r="G95" s="208" t="s">
-        <v>214</v>
-      </c>
-      <c r="H95" s="208" t="s">
-        <v>228</v>
-      </c>
-      <c r="I95" s="208">
-        <v>24</v>
-      </c>
-      <c r="J95" s="208" t="s">
+      <c r="J95" s="193" t="s">
         <v>31</v>
       </c>
     </row>
